--- a/master/result/19_重生逆袭：女王归来/19_逆袭女王.xlsx
+++ b/master/result/19_重生逆袭：女王归来/19_逆袭女王.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>January</v>
       </c>
       <c r="B2" t="str">
-        <v>January</v>
+        <v>/January/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>一月</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>female</v>
       </c>
       <c r="B3" t="str">
-        <v>female</v>
+        <v>/female/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>女性</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>southeast</v>
       </c>
       <c r="B4" t="str">
-        <v>southeast</v>
+        <v>/southeast/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>东南</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>origin</v>
       </c>
       <c r="B5" t="str">
-        <v>origin</v>
+        <v>/origin/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>出身</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>deprive</v>
       </c>
       <c r="B6" t="str">
-        <v>deprive</v>
+        <v>/deprive/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>剥夺</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>average</v>
       </c>
       <c r="B7" t="str">
-        <v>average</v>
+        <v>/average/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>普通</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>destructive</v>
       </c>
       <c r="B8" t="str">
-        <v>destructive</v>
+        <v>/destructive/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>破坏性</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>portable</v>
       </c>
       <c r="B9" t="str">
-        <v>portable</v>
+        <v>/portable/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>轻便</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>western</v>
       </c>
       <c r="B10" t="str">
-        <v>western</v>
+        <v>/western/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>西方</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>pact</v>
       </c>
       <c r="B11" t="str">
-        <v>pact</v>
+        <v>/pact/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>条约</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>group</v>
       </c>
       <c r="B12" t="str">
-        <v>group</v>
+        <v>/group/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>组</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>export</v>
       </c>
       <c r="B13" t="str">
-        <v>export</v>
+        <v>/ɪkˈspɔːt/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>出口</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>journey</v>
       </c>
       <c r="B14" t="str">
-        <v>journey</v>
+        <v>/journey/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>旅程</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>capable</v>
       </c>
       <c r="B15" t="str">
-        <v>capable</v>
+        <v>/ˈkeɪpəbəl/</v>
       </c>
       <c r="C15" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>有能力</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>sofa</v>
       </c>
       <c r="B16" t="str">
-        <v>sofa</v>
+        <v>/sofa/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>沙发</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>profitable</v>
       </c>
       <c r="B17" t="str">
-        <v>profitable</v>
+        <v>/profitable/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>有利可图</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>foresee</v>
       </c>
       <c r="B18" t="str">
-        <v>foresee</v>
+        <v>/foresee/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>预见</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>utmost</v>
       </c>
       <c r="B19" t="str">
-        <v>utmost</v>
+        <v>/utmost/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>最大</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>turnover</v>
       </c>
       <c r="B20" t="str">
-        <v>turnover</v>
+        <v>/turnover/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>周转</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>goods</v>
       </c>
       <c r="B21" t="str">
-        <v>goods</v>
+        <v>/goods/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>商品</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>preferable</v>
       </c>
       <c r="B22" t="str">
-        <v>preferable</v>
+        <v>/preferable/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>更可取的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>crime</v>
       </c>
       <c r="B23" t="str">
-        <v>crime</v>
+        <v>/kraɪm/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>犯罪</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>salute</v>
       </c>
       <c r="B24" t="str">
-        <v>salute</v>
+        <v>/salute/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>敬礼</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>courage</v>
       </c>
       <c r="B25" t="str">
-        <v>courage</v>
+        <v>/ˈkʌrɪdʒ/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>勇气</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>develop</v>
       </c>
       <c r="B26" t="str">
-        <v>develop</v>
+        <v>/dɪˈveləp/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>发展</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>adolescent</v>
       </c>
       <c r="B27" t="str">
-        <v>adolescent</v>
+        <v>/adolescent/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>青少年</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>court</v>
       </c>
       <c r="B28" t="str">
-        <v>court</v>
+        <v>/kɔːt/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>法院</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>influence</v>
       </c>
       <c r="B29" t="str">
-        <v>influence</v>
+        <v>/ˈɪnfluəns/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>影响</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>noisy</v>
       </c>
       <c r="B30" t="str">
-        <v>noisy</v>
+        <v>/noisy/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>喧闹</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>declaration</v>
       </c>
       <c r="B31" t="str">
-        <v>declaration</v>
+        <v>/declaration/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>宣布</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>recruit</v>
       </c>
       <c r="B32" t="str">
-        <v>recruit</v>
+        <v>/recruit/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>招募</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>tradition</v>
       </c>
       <c r="B33" t="str">
-        <v>tradition</v>
+        <v>/tradition/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>传统</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>refugee</v>
       </c>
       <c r="B34" t="str">
-        <v>refugee</v>
+        <v>/refugee/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>难民</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>scientist</v>
       </c>
       <c r="B35" t="str">
-        <v>scientist</v>
+        <v>/scientist/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>科学家</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>preposition</v>
       </c>
       <c r="B36" t="str">
-        <v>preposition</v>
+        <v>/preposition/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>介词</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>common</v>
       </c>
       <c r="B37" t="str">
-        <v>common</v>
+        <v>/ˈkɒmən/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>普通</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>overlap</v>
       </c>
       <c r="B38" t="str">
-        <v>overlap</v>
+        <v>/overlap/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>重叠</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>solution</v>
       </c>
       <c r="B39" t="str">
+        <v>/solution/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>解决方案</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>pneumonia</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/pneumonia/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>肺炎</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>lick</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/lick/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>舔</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>delay</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/dɪˈleɪ/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>延迟</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>hamburger</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/hamburger/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>汉堡</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>infant</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/infant/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>婴儿</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>ninety</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/ninety/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>九十</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
         <v>solution</v>
       </c>
-      <c r="C39" t="str">
-        <v>解决方案</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>pneumonia</v>
-      </c>
-      <c r="C40" t="str">
-        <v>肺炎</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>lick</v>
-      </c>
-      <c r="C41" t="str">
-        <v>舔</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>delay</v>
-      </c>
-      <c r="C42" t="str">
-        <v>延迟</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>hamburger</v>
-      </c>
-      <c r="C43" t="str">
-        <v>汉堡</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>infant</v>
-      </c>
-      <c r="C44" t="str">
-        <v>婴儿</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>ninety</v>
-      </c>
-      <c r="C45" t="str">
-        <v>九十</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
       <c r="B46" t="str">
-        <v>solution</v>
+        <v>/solution/</v>
       </c>
       <c r="C46" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>解决办法</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>institute</v>
       </c>
       <c r="B47" t="str">
-        <v>institute</v>
+        <v>/institute/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>学院</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>crack</v>
       </c>
       <c r="B48" t="str">
-        <v>crack</v>
+        <v>/kræk/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>缝隙</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>worship</v>
       </c>
       <c r="B49" t="str">
-        <v>worship</v>
+        <v>/worship/</v>
       </c>
       <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>崇拜</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>tomb</v>
       </c>
       <c r="B50" t="str">
-        <v>tomb</v>
+        <v>/tomb/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>坟墓</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>penny</v>
       </c>
       <c r="B51" t="str">
-        <v>penny</v>
+        <v>/penny/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>便士</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>